--- a/src/plano-de-aulas.xlsx
+++ b/src/plano-de-aulas.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="0"/>
+  <workbookPr dateCompatibility="0"/>
   <workbookProtection/>
   <bookViews>
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
   <si>
     <t>Data</t>
   </si>
@@ -131,6 +131,12 @@
 Discussão: algoritmo quicksort. Ref Cormen Cap 7</t>
   </si>
   <si>
+    <t xml:space="preserve">Quiz em duplas + Estudos para prova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEMANA AI</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ordenando rápido (sempre)</t>
   </si>
   <si>
@@ -138,12 +144,6 @@
 Discussão: algoritmo mergesort
 Implementações
 Ref Cormen cap 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quiz em duplas + Estudos para prova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEMANA AI</t>
   </si>
   <si>
     <t xml:space="preserve">Primeiro problema de enumeração exaustiva</t>
@@ -199,6 +199,9 @@
 Implementação do algoritmo usando testes de unidade. Ref Skiena Cap 7</t>
   </si>
   <si>
+    <t xml:space="preserve">QUIZ NESSA SEMANA SOBRE RECURSÃO USANDO AULA CANCELADA!</t>
+  </si>
+  <si>
     <t xml:space="preserve">Caminhos em um Labirinto</t>
   </si>
   <si>
@@ -207,9 +210,6 @@
   <si>
     <t xml:space="preserve">Representação do Labirinto usando Matriz
 "Algoritmo da mão direita": desenvolver método inicial para sair do labirinto e implementar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUIZ NESSA SEMANA SOBRE RECURSÃO USANDO AULA CANCELADA!</t>
   </si>
   <si>
     <t xml:space="preserve">Como encontrar um caminho até o destino?</t>
@@ -280,9 +280,6 @@
 Aluno faz Implementação com testes de unidade
 Ref Cormen cap 22</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Prática de problemas recomendados no leetcode</t>
   </si>
   <si>
     <r>
@@ -711,7 +708,7 @@
     </font>
     <font>
       <sz val="11.000000"/>
-      <color theme="0" tint="0"/>
+      <color theme="0"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -725,7 +722,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -759,7 +756,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
-        <bgColor rgb="FFC00000"/>
+        <bgColor rgb="FF9C0006"/>
       </patternFill>
     </fill>
     <fill>
@@ -784,12 +781,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFD7D7"/>
         <bgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor rgb="FF9C0006"/>
       </patternFill>
     </fill>
     <fill>
@@ -823,7 +814,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -865,28 +856,6 @@
       <left style="thin">
         <color theme="1"/>
       </left>
-      <right style="none"/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
       <right style="thin">
         <color theme="1"/>
       </right>
@@ -918,7 +887,7 @@
       <protection hidden="0" locked="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="39">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -939,15 +908,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="6" fillId="6" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="6" fillId="6" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="6" fillId="6" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf fontId="6" fillId="6" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -964,14 +925,6 @@
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -998,10 +951,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -1020,7 +969,7 @@
     <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="6" applyFont="1" applyFill="1" applyProtection="1">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="11" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -1028,16 +977,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="12" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="0" fillId="11" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="12" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="0" fillId="11" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="12" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="0" fillId="11" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="12" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="13" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="1">
@@ -1046,14 +998,11 @@
     <xf fontId="0" fillId="14" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="15" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="14" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf fontId="0" fillId="13" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="16" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="1">
+    <xf fontId="0" fillId="15" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -1642,7 +1591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="13.800000000000001">
+    <row r="4" ht="14.25">
       <c r="A4" s="3">
         <f t="shared" ref="A4:A7" si="0">A2+7</f>
         <v>46069</v>
@@ -1651,22 +1600,22 @@
       <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
-    </row>
-    <row r="5" ht="13.800000000000001">
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" ht="14.25">
       <c r="A5" s="3">
         <f t="shared" si="0"/>
         <v>46071</v>
       </c>
-      <c r="B5" s="9"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" ht="85.5">
       <c r="A6" s="3">
@@ -1679,13 +1628,13 @@
       <c r="C6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1694,19 +1643,19 @@
         <f t="shared" si="0"/>
         <v>46078</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="9">
         <v>4</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="12" t="s">
+      <c r="E7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1715,17 +1664,17 @@
         <f>A6 + 7</f>
         <v>46083</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="13" t="s">
+      <c r="B8" s="9"/>
+      <c r="C8" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="13" t="s">
+      <c r="E8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1734,13 +1683,13 @@
         <f>A7+7</f>
         <v>46085</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="9">
         <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="5" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -1749,26 +1698,26 @@
       <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="11"/>
     </row>
     <row r="10" ht="98.5" customHeight="1">
       <c r="A10" s="3">
         <f>A8 + 7</f>
         <v>46090</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="9">
         <v>6</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="17" t="s">
+      <c r="E10" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1801,19 +1750,6 @@
       <c r="B12" s="4">
         <v>8</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="1"/>
     </row>
     <row r="13" ht="99.950000000000003" customHeight="1">
       <c r="A13" s="3">
@@ -1824,7 +1760,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -1836,71 +1772,71 @@
         <v>46104</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="19"/>
+      <c r="C14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="15"/>
     </row>
     <row r="15" ht="93.75" customHeight="1">
       <c r="A15" s="3">
         <f>A13+7</f>
         <v>46106</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="9">
         <v>10</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="19"/>
+      <c r="C15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="15"/>
     </row>
     <row r="16" ht="106.7" customHeight="1">
       <c r="A16" s="3">
         <f>A14 + 7</f>
         <v>46111</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="1"/>
     </row>
     <row r="17" ht="138.80000000000001" customHeight="1">
       <c r="A17" s="3">
         <f t="shared" ref="A17:A18" si="1">A15+7</f>
         <v>46113</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>38</v>
+      <c r="B17" s="15"/>
+      <c r="C17" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="L17" s="1"/>
     </row>
@@ -1909,20 +1845,20 @@
         <f t="shared" si="1"/>
         <v>46118</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="9">
         <v>11</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>40</v>
+      <c r="D18" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="L18" s="1"/>
     </row>
@@ -1931,20 +1867,20 @@
         <f>A17 + 7</f>
         <v>46120</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="9">
         <v>12</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>42</v>
+      <c r="D19" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="L19" s="1"/>
     </row>
@@ -1953,23 +1889,23 @@
         <f>A18+7</f>
         <v>46125</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="9">
         <v>13</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="21" ht="127.59999999999999" customHeight="1">
@@ -1977,20 +1913,20 @@
         <f>A19 + 7</f>
         <v>46127</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="9">
         <v>14</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L21" s="1"/>
     </row>
@@ -2005,10 +1941,9 @@
       <c r="C22" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="1"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
       <c r="L22" s="1"/>
     </row>
     <row r="23" ht="202.19999999999999" customHeight="1">
@@ -2016,20 +1951,20 @@
         <f>A21 + 7</f>
         <v>46134</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="9">
         <v>16</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="13" t="s">
+      <c r="C23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>49</v>
+      <c r="E23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="24" ht="99.25" customHeight="1">
@@ -2037,20 +1972,20 @@
         <f>A22+7</f>
         <v>46139</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="9">
         <v>17</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="13" t="s">
+      <c r="C24" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E24" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>50</v>
+      <c r="E24" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="25" ht="112.65000000000001" customHeight="1">
@@ -2058,15 +1993,21 @@
         <f>A23 + 7</f>
         <v>46141</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="9">
         <v>18</v>
       </c>
-      <c r="C25" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="13"/>
+      <c r="C25" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="L25" s="1"/>
     </row>
     <row r="26" ht="167.15000000000001" customHeight="1">
@@ -2074,20 +2015,20 @@
         <f>A24+7</f>
         <v>46146</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="9">
         <v>19</v>
       </c>
-      <c r="C26" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="13" t="s">
+      <c r="C26" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>52</v>
+      <c r="E26" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="27" ht="94" customHeight="1">
@@ -2095,11 +2036,11 @@
         <f>A25 + 7</f>
         <v>46148</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="9">
         <v>20</v>
       </c>
-      <c r="C27" s="14" t="s">
-        <v>32</v>
+      <c r="C27" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -2110,17 +2051,17 @@
         <f>A26+7</f>
         <v>46153</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="9">
         <v>21</v>
       </c>
-      <c r="C28" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="C28" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
     </row>
     <row r="29" ht="79.099999999999994" customHeight="1">
       <c r="A29" s="3">
@@ -2130,24 +2071,24 @@
       <c r="B29" s="4">
         <v>22</v>
       </c>
-      <c r="C29" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="C29" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
     </row>
     <row r="30" ht="89.549999999999997" customHeight="1">
-      <c r="A30" s="22"/>
+      <c r="A30" s="17"/>
       <c r="B30" s="4">
         <v>23</v>
       </c>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
     </row>
     <row r="31" ht="69.400000000000006" customHeight="1">
       <c r="A31" s="3"/>
@@ -2156,12 +2097,12 @@
       </c>
     </row>
     <row r="32" ht="13.800000000000001" customHeight="1">
-      <c r="A32" s="22"/>
-      <c r="B32" s="19"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="15"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="22"/>
-      <c r="B33" s="19"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2270,13 +2211,13 @@
       <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2285,17 +2226,17 @@
         <f t="shared" si="2"/>
         <v>45889</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="13" t="s">
+      <c r="E5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2307,16 +2248,16 @@
       <c r="B6" s="4">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="13" t="s">
+      <c r="E6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2325,7 +2266,7 @@
         <f t="shared" si="2"/>
         <v>45896</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="9">
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -2346,36 +2287,36 @@
         <f>A6 + 7</f>
         <v>45901</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
     </row>
     <row r="9" ht="81.75" customHeight="1">
       <c r="A9" s="3">
         <f>A7+7</f>
         <v>45903</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="9">
         <v>5</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="17" t="s">
+      <c r="E9" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="15" t="s">
-        <v>55</v>
+      <c r="G9" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="10" ht="98.5" customHeight="1">
@@ -2383,7 +2324,7 @@
         <f>A8 + 7</f>
         <v>45908</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="9">
         <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -2411,13 +2352,13 @@
         <v>22</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" ht="101.25" customHeight="1">
@@ -2432,16 +2373,16 @@
         <v>22</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" ht="99.950000000000003" customHeight="1">
@@ -2453,16 +2394,16 @@
         <v>9</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="14" ht="99.950000000000003" customHeight="1">
@@ -2471,70 +2412,70 @@
         <v>45922</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="19"/>
+      <c r="C14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="15"/>
     </row>
     <row r="15" ht="93.75" customHeight="1">
       <c r="A15" s="3">
         <f>A13+7</f>
         <v>45924</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="9">
         <v>10</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="19"/>
+      <c r="C15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="15"/>
     </row>
     <row r="16" ht="106.7" customHeight="1">
       <c r="A16" s="3">
         <f>A14 + 7</f>
         <v>45929</v>
       </c>
-      <c r="B16" s="19"/>
+      <c r="B16" s="15"/>
       <c r="C16" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="15"/>
+        <v>33</v>
+      </c>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" ht="138.80000000000001" customHeight="1">
       <c r="A17" s="3">
         <f t="shared" ref="A17:A18" si="3">A15+7</f>
         <v>45931</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="13" t="s">
+      <c r="B17" s="15"/>
+      <c r="C17" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="13" t="s">
+      <c r="D17" s="10"/>
+      <c r="E17" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>35</v>
       </c>
       <c r="L17" s="1"/>
@@ -2544,19 +2485,19 @@
         <f t="shared" si="3"/>
         <v>45936</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="9">
         <v>11</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="13" t="s">
+      <c r="E18" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="10" t="s">
         <v>38</v>
       </c>
       <c r="L18" s="1"/>
@@ -2566,19 +2507,19 @@
         <f>A17 + 7</f>
         <v>45938</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="9">
         <v>12</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="13" t="s">
+      <c r="E19" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="10" t="s">
         <v>40</v>
       </c>
       <c r="L19" s="1"/>
@@ -2588,23 +2529,23 @@
         <f>A18+7</f>
         <v>45943</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="9">
         <v>13</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="13" t="s">
+      <c r="E20" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="10" t="s">
         <v>42</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" ht="127.59999999999999" customHeight="1">
@@ -2612,20 +2553,20 @@
         <f>A19 + 7</f>
         <v>45945</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="9">
         <v>14</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L21" s="1"/>
     </row>
@@ -2637,17 +2578,17 @@
       <c r="B22" s="4">
         <v>15</v>
       </c>
-      <c r="C22" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>60</v>
+      <c r="C22" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>59</v>
       </c>
       <c r="L22" s="1"/>
     </row>
@@ -2656,11 +2597,11 @@
         <f>A21 + 7</f>
         <v>45952</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="9">
         <v>16</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>47</v>
@@ -2677,19 +2618,19 @@
         <f>A22+7</f>
         <v>45957</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="9">
         <v>17</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="13" t="s">
+      <c r="C24" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E24" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="13" t="s">
+      <c r="E24" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="10" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2698,19 +2639,19 @@
         <f>A23 + 7</f>
         <v>45959</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="9">
         <v>18</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="13" t="s">
+      <c r="C25" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="13" t="s">
+      <c r="E25" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="10" t="s">
         <v>50</v>
       </c>
       <c r="L25" s="1"/>
@@ -2720,20 +2661,20 @@
         <f>A24+7</f>
         <v>45964</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="9">
         <v>19</v>
       </c>
-      <c r="C26" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="13" t="s">
+      <c r="C26" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>52</v>
+      <c r="E26" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="27" ht="94" customHeight="1">
@@ -2741,32 +2682,32 @@
         <f>A25 + 7</f>
         <v>45966</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="9">
         <v>20</v>
       </c>
-      <c r="C27" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
+      <c r="C27" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
     </row>
     <row r="28" ht="55.950000000000003" customHeight="1">
       <c r="A28" s="3">
         <f>A26+7</f>
         <v>45971</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="9">
         <v>21</v>
       </c>
-      <c r="C28" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="C28" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
     </row>
     <row r="29" ht="79.099999999999994" customHeight="1">
       <c r="A29" s="3">
@@ -2776,17 +2717,17 @@
       <c r="B29" s="4">
         <v>22</v>
       </c>
-      <c r="C29" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="C29" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
     </row>
     <row r="30" ht="89.549999999999997" customHeight="1">
-      <c r="A30" s="22"/>
+      <c r="A30" s="17"/>
       <c r="B30" s="4">
         <v>23</v>
       </c>
@@ -2798,12 +2739,12 @@
       </c>
     </row>
     <row r="32" ht="13.800000000000001" customHeight="1">
-      <c r="A32" s="22"/>
-      <c r="B32" s="19"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="15"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="22"/>
-      <c r="B33" s="19"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2858,7 +2799,7 @@
       </c>
     </row>
     <row r="2" ht="68.650000000000006">
-      <c r="A2" s="22">
+      <c r="A2" s="17">
         <v>45693</v>
       </c>
       <c r="B2" s="4">
@@ -2878,7 +2819,7 @@
       </c>
     </row>
     <row r="3" ht="55.200000000000003">
-      <c r="A3" s="22">
+      <c r="A3" s="17">
         <v>45695</v>
       </c>
       <c r="B3" s="4">
@@ -2898,7 +2839,7 @@
       </c>
     </row>
     <row r="4" ht="82.049999999999997">
-      <c r="A4" s="22">
+      <c r="A4" s="17">
         <f t="shared" ref="A4:A7" si="4">A2+7</f>
         <v>45700</v>
       </c>
@@ -2906,62 +2847,62 @@
       <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" ht="135.80000000000001">
-      <c r="A5" s="22">
+      <c r="A5" s="17">
         <f t="shared" si="4"/>
         <v>45702</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="13" t="s">
+      <c r="E5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" ht="135.80000000000001">
-      <c r="A6" s="22">
+      <c r="A6" s="17">
         <f t="shared" si="4"/>
         <v>45707</v>
       </c>
       <c r="B6" s="4">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="13" t="s">
+      <c r="E6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" ht="95.5">
-      <c r="A7" s="22">
+      <c r="A7" s="17">
         <f t="shared" si="4"/>
         <v>45709</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="9">
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -2974,63 +2915,63 @@
         <v>8</v>
       </c>
       <c r="F7" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" ht="57" customHeight="1">
+      <c r="A8" s="20" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="8" ht="57" customHeight="1">
-      <c r="A8" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="11"/>
+      <c r="B8" s="9"/>
       <c r="C8" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
     <row r="9" ht="81.75" customHeight="1">
-      <c r="A9" s="22">
+      <c r="A9" s="17">
         <f t="shared" ref="A9:A10" si="5">A6+7</f>
         <v>45714</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="9">
         <v>5</v>
       </c>
-      <c r="C9" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
+      <c r="C9" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
     </row>
     <row r="10" ht="98.5" customHeight="1">
-      <c r="A10" s="22">
+      <c r="A10" s="17">
         <f t="shared" si="5"/>
         <v>45716</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="9">
         <v>6</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
     </row>
     <row r="11" ht="65.650000000000006" customHeight="1">
-      <c r="A11" s="22">
+      <c r="A11" s="17">
         <f>A9+7</f>
         <v>45721</v>
       </c>
       <c r="B11" s="4">
         <v>7</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
     </row>
     <row r="12" ht="101.25" customHeight="1">
       <c r="B12" s="4">
@@ -3050,7 +2991,7 @@
       </c>
     </row>
     <row r="13" ht="99.950000000000003" customHeight="1">
-      <c r="A13" s="22">
+      <c r="A13" s="17">
         <f>A10+7</f>
         <v>45723</v>
       </c>
@@ -3061,395 +3002,395 @@
         <v>22</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" ht="99.950000000000003" customHeight="1">
-      <c r="A14" s="26" t="s">
-        <v>65</v>
+      <c r="A14" s="21" t="s">
+        <v>64</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="13" t="s">
+      <c r="E14" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="15" ht="93.75" customHeight="1">
-      <c r="A15" s="22">
+      <c r="A15" s="17">
         <f>A11+7</f>
         <v>45728</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="9">
         <v>10</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>66</v>
+      <c r="E15" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="74.599999999999994" customHeight="1">
-      <c r="A16" s="22">
+      <c r="A16" s="17">
         <f>A13+7</f>
         <v>45730</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="13" t="s">
+      <c r="B16" s="15"/>
+      <c r="C16" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>68</v>
-      </c>
     </row>
     <row r="17" ht="81.299999999999997" customHeight="1">
-      <c r="A17" s="22">
+      <c r="A17" s="17">
         <f t="shared" ref="A17:A33" si="6">A15+7</f>
         <v>45735</v>
       </c>
-      <c r="B17" s="19"/>
+      <c r="B17" s="15"/>
       <c r="C17" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="18" ht="103.7" customHeight="1">
-      <c r="A18" s="22">
+      <c r="A18" s="17">
         <f t="shared" si="6"/>
         <v>45737</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="9">
         <v>11</v>
       </c>
-      <c r="C18" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="19"/>
+      <c r="C18" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="15"/>
     </row>
     <row r="19" ht="79.5" customHeight="1">
-      <c r="A19" s="22">
+      <c r="A19" s="17">
         <f t="shared" si="6"/>
         <v>45742</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="9">
         <v>12</v>
       </c>
-      <c r="C19" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="19"/>
+      <c r="C19" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="15"/>
     </row>
     <row r="20" ht="93" customHeight="1">
-      <c r="A20" s="22">
+      <c r="A20" s="17">
         <f t="shared" si="6"/>
         <v>45744</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="9">
         <v>13</v>
       </c>
-      <c r="C20" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="19"/>
+      <c r="C20" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="15"/>
     </row>
     <row r="21" ht="106.5" customHeight="1">
-      <c r="A21" s="22">
+      <c r="A21" s="17">
         <f t="shared" si="6"/>
         <v>45749</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="9">
         <v>14</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="13" t="s">
+      <c r="C21" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="E21" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="13" t="s">
+      <c r="D21" s="10" t="s">
         <v>45</v>
       </c>
+      <c r="E21" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="22" ht="144.75" customHeight="1">
-      <c r="A22" s="22">
+      <c r="A22" s="17">
         <f t="shared" si="6"/>
         <v>45751</v>
       </c>
       <c r="B22" s="4">
         <v>15</v>
       </c>
-      <c r="C22" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="13" t="s">
+      <c r="C22" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>69</v>
+      <c r="E22" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="23" ht="112.65000000000001" customHeight="1">
-      <c r="A23" s="22">
+      <c r="A23" s="17">
         <f t="shared" si="6"/>
         <v>45756</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="9">
         <v>16</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="13" t="s">
+      <c r="C23" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>70</v>
+      <c r="E23" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="24" ht="99.25" customHeight="1">
-      <c r="A24" s="22">
+      <c r="A24" s="17">
         <f t="shared" si="6"/>
         <v>45758</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="9">
         <v>17</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="13" t="s">
+      <c r="C24" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E24" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>70</v>
+      <c r="E24" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="112.65000000000001" customHeight="1">
-      <c r="A25" s="22">
+      <c r="A25" s="17">
         <f t="shared" si="6"/>
         <v>45763</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="9">
         <v>18</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="13" t="s">
+      <c r="C25" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E25" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="26" ht="106.7" customHeight="1">
-      <c r="A26" s="22">
+      <c r="A26" s="17">
         <f t="shared" si="6"/>
         <v>45765</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="9">
         <v>19</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
     </row>
     <row r="27" ht="94" customHeight="1">
-      <c r="A27" s="22">
+      <c r="A27" s="17">
         <f t="shared" si="6"/>
         <v>45770</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="9">
         <v>20</v>
       </c>
-      <c r="C27" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="13" t="s">
+      <c r="C27" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="28" ht="55.950000000000003" customHeight="1">
-      <c r="A28" s="22">
+      <c r="A28" s="17">
         <f t="shared" si="6"/>
         <v>45772</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="9">
         <v>21</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D28" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="29" ht="79.099999999999994" customHeight="1">
-      <c r="A29" s="22">
+      <c r="A29" s="17">
         <f t="shared" si="6"/>
         <v>45777</v>
       </c>
       <c r="B29" s="4">
         <v>22</v>
       </c>
-      <c r="C29" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D29" s="10" t="s">
+      <c r="C29" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>75</v>
+      <c r="F29" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="30" ht="89.549999999999997" customHeight="1">
-      <c r="A30" s="22">
+      <c r="A30" s="17">
         <f t="shared" si="6"/>
         <v>45779</v>
       </c>
       <c r="B30" s="4">
         <v>23</v>
       </c>
-      <c r="C30" s="27" t="s">
+      <c r="C30" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
     </row>
     <row r="31" ht="69.400000000000006" customHeight="1">
-      <c r="A31" s="22">
+      <c r="A31" s="17">
         <f t="shared" si="6"/>
         <v>45784</v>
       </c>
       <c r="B31" s="4">
         <v>24</v>
       </c>
-      <c r="C31" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="D31" s="30" t="s">
+      <c r="C31" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="E31" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="30" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="32" ht="13.800000000000001" customHeight="1">
-      <c r="A32" s="22">
+      <c r="A32" s="17">
         <f t="shared" si="6"/>
         <v>45786</v>
       </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="22">
+      <c r="A33" s="17">
         <f t="shared" si="6"/>
         <v>45791</v>
       </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3508,7 +3449,7 @@
       <c r="I1" s="2"/>
     </row>
     <row r="2" ht="68.650000000000006">
-      <c r="A2" s="22">
+      <c r="A2" s="17">
         <v>45511</v>
       </c>
       <c r="B2" s="4">
@@ -3526,12 +3467,12 @@
       <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="32" t="s">
-        <v>78</v>
+      <c r="G2" s="27" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="3" ht="55.200000000000003">
-      <c r="A3" s="22">
+      <c r="A3" s="17">
         <v>45513</v>
       </c>
       <c r="B3" s="4">
@@ -3549,78 +3490,78 @@
       <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="32"/>
+      <c r="G3" s="27"/>
     </row>
     <row r="4" ht="82.049999999999997">
-      <c r="A4" s="22">
+      <c r="A4" s="17">
         <f t="shared" ref="A4:A11" si="7">A2+7</f>
         <v>45518</v>
       </c>
-      <c r="B4" s="9"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="32"/>
+      <c r="G4" s="27"/>
     </row>
     <row r="5" ht="135.80000000000001">
-      <c r="A5" s="22">
+      <c r="A5" s="17">
         <f t="shared" si="7"/>
         <v>45520</v>
       </c>
       <c r="B5" s="4">
         <v>3</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="13" t="s">
+      <c r="E5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="32"/>
+      <c r="G5" s="27"/>
     </row>
     <row r="6" ht="135.80000000000001">
-      <c r="A6" s="22">
+      <c r="A6" s="17">
         <f t="shared" si="7"/>
         <v>45525</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="9">
         <v>4</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="13" t="s">
+      <c r="E6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="32"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7" ht="95.5">
-      <c r="A7" s="22">
+      <c r="A7" s="17">
         <f t="shared" si="7"/>
         <v>45527</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="9">
         <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -3633,16 +3574,16 @@
         <v>8</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="32"/>
+        <v>61</v>
+      </c>
+      <c r="G7" s="27"/>
     </row>
     <row r="8" ht="98.5" customHeight="1">
-      <c r="A8" s="22">
+      <c r="A8" s="17">
         <f t="shared" si="7"/>
         <v>45532</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -3657,10 +3598,10 @@
       <c r="F8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="32"/>
+      <c r="G8" s="27"/>
     </row>
     <row r="9" ht="65.650000000000006" customHeight="1">
-      <c r="A9" s="22">
+      <c r="A9" s="17">
         <f t="shared" si="7"/>
         <v>45534</v>
       </c>
@@ -3671,73 +3612,73 @@
         <v>22</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="32"/>
+        <v>33</v>
+      </c>
+      <c r="G9" s="27"/>
     </row>
     <row r="10" ht="101.25" customHeight="1">
-      <c r="A10" s="22">
+      <c r="A10" s="17">
         <f t="shared" si="7"/>
         <v>45539</v>
       </c>
       <c r="B10" s="4">
         <v>8</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="13" t="s">
+      <c r="E10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="33" t="s">
-        <v>79</v>
+      <c r="G10" s="28" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="11" ht="99.950000000000003" customHeight="1">
-      <c r="A11" s="22">
+      <c r="A11" s="17">
         <f t="shared" si="7"/>
         <v>45541</v>
       </c>
       <c r="B11" s="4">
         <v>9</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>80</v>
+      <c r="E11" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="12" ht="75" customHeight="1">
-      <c r="A12" s="22">
+      <c r="A12" s="17">
         <f t="shared" ref="A12:A30" si="8">A10+7</f>
         <v>45546</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="9">
         <v>10</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="8" t="s">
         <v>25</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -3749,383 +3690,383 @@
       <c r="F12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="34" t="s">
-        <v>81</v>
+      <c r="G12" s="29" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="13" ht="74.599999999999994" customHeight="1">
-      <c r="A13" s="22">
+      <c r="A13" s="17">
         <f t="shared" si="8"/>
         <v>45548</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="13" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" s="35" t="s">
-        <v>82</v>
+      <c r="G13" s="30" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="14" ht="81.299999999999997" customHeight="1">
-      <c r="A14" s="22">
+      <c r="A14" s="17">
         <f t="shared" si="8"/>
         <v>45553</v>
       </c>
-      <c r="B14" s="19"/>
+      <c r="B14" s="15"/>
       <c r="C14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="15" ht="103.7" customHeight="1">
-      <c r="A15" s="22">
+      <c r="A15" s="17">
         <f t="shared" si="8"/>
         <v>45555</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="9">
         <v>11</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="19"/>
+      <c r="C15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="15"/>
     </row>
     <row r="16" ht="79.5" customHeight="1">
-      <c r="A16" s="22">
+      <c r="A16" s="17">
         <f t="shared" si="8"/>
         <v>45560</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="9">
         <v>12</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="19"/>
+      <c r="C16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="15"/>
     </row>
     <row r="17" ht="93" customHeight="1">
-      <c r="A17" s="22">
+      <c r="A17" s="17">
         <f t="shared" si="8"/>
         <v>45562</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="9">
         <v>13</v>
       </c>
-      <c r="C17" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="13" t="s">
+      <c r="C17" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="13" t="s">
+      <c r="D17" s="10" t="s">
         <v>45</v>
       </c>
+      <c r="E17" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="18" ht="122.34999999999999">
-      <c r="A18" s="22">
+      <c r="A18" s="17">
         <f t="shared" si="8"/>
         <v>45567</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="9">
         <v>14</v>
       </c>
-      <c r="C18" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="13" t="s">
+      <c r="C18" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>69</v>
+      <c r="E18" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="19" ht="98.5" customHeight="1">
-      <c r="A19" s="22">
+      <c r="A19" s="17">
         <f t="shared" si="8"/>
         <v>45569</v>
       </c>
       <c r="B19" s="4">
         <v>15</v>
       </c>
-      <c r="C19" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="13" t="s">
+      <c r="C19" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="13" t="s">
+      <c r="E19" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="G19" s="33" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="20" ht="112.65000000000001" customHeight="1">
-      <c r="A20" s="22">
+      <c r="A20" s="17">
         <f t="shared" si="8"/>
         <v>45574</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="9">
         <v>16</v>
       </c>
-      <c r="C20" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>85</v>
+      <c r="C20" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="99.25" customHeight="1">
-      <c r="A21" s="22">
+      <c r="A21" s="17">
         <f t="shared" si="8"/>
         <v>45576</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="9">
         <v>17</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>74</v>
+      <c r="C21" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="22" ht="112.65000000000001" customHeight="1">
-      <c r="A22" s="22">
+      <c r="A22" s="17">
         <f t="shared" si="8"/>
         <v>45581</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="9">
         <v>18</v>
       </c>
-      <c r="C22" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="13" t="s">
+      <c r="C22" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="23" ht="106.7" customHeight="1">
-      <c r="A23" s="22">
+      <c r="A23" s="17">
         <f t="shared" si="8"/>
         <v>45583</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="9">
         <v>19</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="13" t="s">
+      <c r="C23" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E23" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G23" s="33" t="s">
-        <v>86</v>
+      <c r="G23" s="28" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="24" ht="94" customHeight="1">
-      <c r="A24" s="22">
+      <c r="A24" s="17">
         <f t="shared" si="8"/>
         <v>45588</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="9">
         <v>20</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>85</v>
+      <c r="C24" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="25" ht="55.950000000000003" customHeight="1">
-      <c r="A25" s="22">
+      <c r="A25" s="17">
         <f t="shared" si="8"/>
         <v>45590</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="9">
         <v>21</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G25" s="36" t="s">
-        <v>87</v>
+      <c r="G25" s="31" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="26" ht="79.099999999999994" customHeight="1">
-      <c r="A26" s="22">
+      <c r="A26" s="17">
         <f t="shared" si="8"/>
         <v>45595</v>
       </c>
       <c r="B26" s="4">
         <v>22</v>
       </c>
-      <c r="C26" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D26" s="10" t="s">
+      <c r="C26" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="G26" s="36" t="s">
-        <v>87</v>
+      <c r="F26" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" s="31" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="27" ht="89.549999999999997" customHeight="1">
-      <c r="A27" s="22">
+      <c r="A27" s="17">
         <f t="shared" si="8"/>
         <v>45597</v>
       </c>
       <c r="B27" s="4">
         <v>23</v>
       </c>
-      <c r="C27" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D27" s="10" t="s">
+      <c r="C27" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G27" s="36" t="s">
-        <v>87</v>
+      <c r="G27" s="31" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="28" ht="69.400000000000006" customHeight="1">
-      <c r="A28" s="22">
+      <c r="A28" s="17">
         <f t="shared" si="8"/>
         <v>45602</v>
       </c>
       <c r="B28" s="4">
         <v>24</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="E28" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="F28" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="29" ht="13.800000000000001" customHeight="1">
-      <c r="A29" s="22">
+      <c r="A29" s="17">
         <f t="shared" si="8"/>
         <v>45604</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="22">
+      <c r="A30" s="17">
         <f t="shared" si="8"/>
         <v>45609</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
     </row>
     <row r="1048574" ht="12.800000000000001"/>
     <row r="1048575" ht="12.800000000000001"/>
@@ -4175,23 +4116,23 @@
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" ht="68.650000000000006">
-      <c r="A2" s="22">
+      <c r="A2" s="17">
         <v>45329</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -4205,13 +4146,13 @@
       </c>
     </row>
     <row r="3" ht="55.200000000000003">
-      <c r="A3" s="22">
+      <c r="A3" s="17">
         <v>45331</v>
       </c>
       <c r="B3" s="4">
         <v>2</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -4225,336 +4166,336 @@
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="22">
+      <c r="A4" s="17">
         <f t="shared" ref="A4:A11" si="9">A2+7</f>
         <v>45336</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="7"/>
+      <c r="C4" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" s="9"/>
+      <c r="E4" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" ht="68.650000000000006">
-      <c r="A5" s="22">
+      <c r="A5" s="17">
         <f t="shared" si="9"/>
         <v>45338</v>
       </c>
       <c r="B5" s="4">
         <v>3</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>92</v>
+      <c r="F5" s="8" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="6" ht="135.80000000000001">
-      <c r="A6" s="22">
+      <c r="A6" s="17">
         <f t="shared" si="9"/>
         <v>45343</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="9">
         <v>4</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>93</v>
+      <c r="F6" s="10" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="7" ht="122.34999999999999">
-      <c r="A7" s="22">
+      <c r="A7" s="17">
         <f t="shared" si="9"/>
         <v>45345</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="9">
         <v>5</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="10" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>94</v>
+      <c r="F7" s="10" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="8" ht="144.75" customHeight="1">
-      <c r="A8" s="22">
+      <c r="A8" s="17">
         <f t="shared" si="9"/>
         <v>45350</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <v>6</v>
       </c>
-      <c r="C8" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="10" t="s">
+      <c r="C8" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>95</v>
+      <c r="F8" s="8" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="9" ht="155.25" customHeight="1">
-      <c r="A9" s="22">
+      <c r="A9" s="17">
         <f t="shared" si="9"/>
         <v>45352</v>
       </c>
       <c r="B9" s="4">
         <v>7</v>
       </c>
-      <c r="C9" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="10" t="s">
+      <c r="C9" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>75</v>
+      <c r="F9" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="10" ht="101.25" customHeight="1">
-      <c r="A10" s="22">
+      <c r="A10" s="17">
         <f t="shared" si="9"/>
         <v>45357</v>
       </c>
       <c r="B10" s="4">
         <v>8</v>
       </c>
-      <c r="C10" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="10" t="s">
+      <c r="C10" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="11" ht="99.950000000000003" customHeight="1">
-      <c r="A11" s="22">
+      <c r="A11" s="17">
         <f t="shared" si="9"/>
         <v>45359</v>
       </c>
       <c r="B11" s="4">
         <v>9</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="12" ht="75" customHeight="1">
-      <c r="A12" s="22">
+      <c r="A12" s="17">
         <f t="shared" ref="A12:A30" si="10">A10+7</f>
         <v>45364</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="9">
         <v>10</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="10" t="s">
         <v>23</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>98</v>
+      <c r="F12" s="10" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="13" ht="74.599999999999994" customHeight="1">
-      <c r="A13" s="22">
+      <c r="A13" s="17">
         <f t="shared" si="10"/>
         <v>45366</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="20" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="10" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="13" t="s">
-        <v>99</v>
+      <c r="F13" s="10" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="14" ht="81.299999999999997" customHeight="1">
-      <c r="A14" s="22">
+      <c r="A14" s="17">
         <f t="shared" si="10"/>
         <v>45371</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="20" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="E14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="15" ht="103.7" customHeight="1">
-      <c r="A15" s="22">
+      <c r="A15" s="17">
         <f t="shared" si="10"/>
         <v>45373</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="9">
         <v>11</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="19"/>
+      <c r="C15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="15"/>
     </row>
     <row r="16" ht="79.5" customHeight="1">
-      <c r="A16" s="22">
+      <c r="A16" s="17">
         <f t="shared" si="10"/>
         <v>45378</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="9">
         <v>12</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="19"/>
+      <c r="C16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="15"/>
     </row>
     <row r="17" ht="93" customHeight="1">
-      <c r="A17" s="22">
+      <c r="A17" s="17">
         <f t="shared" si="10"/>
         <v>45380</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="9">
         <v>13</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17" s="9"/>
+      <c r="E17" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" ht="55.200000000000003">
-      <c r="A18" s="22">
+      <c r="A18" s="17">
         <f t="shared" si="10"/>
         <v>45385</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="9">
         <v>14</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>30</v>
+      <c r="D18" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="13" t="s">
-        <v>100</v>
+      <c r="F18" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="19" ht="28.350000000000001">
-      <c r="A19" s="22">
+      <c r="A19" s="17">
         <f t="shared" si="10"/>
         <v>45387</v>
       </c>
       <c r="B19" s="4">
         <v>15</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>102</v>
-      </c>
     </row>
     <row r="20" ht="72.75" customHeight="1">
-      <c r="A20" s="22">
+      <c r="A20" s="17">
         <f t="shared" si="10"/>
         <v>45392</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="9">
         <v>16</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="5" t="s">
@@ -4568,200 +4509,200 @@
       </c>
     </row>
     <row r="21" ht="68.650000000000006">
-      <c r="A21" s="22">
+      <c r="A21" s="17">
         <f t="shared" si="10"/>
         <v>45394</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="9">
         <v>17</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="13" t="s">
+      <c r="C21" s="16" t="s">
         <v>44</v>
       </c>
+      <c r="D21" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="E21" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>45</v>
+      <c r="F21" s="10" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="22" ht="94" customHeight="1">
-      <c r="A22" s="22">
+      <c r="A22" s="17">
         <f t="shared" si="10"/>
         <v>45399</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="9">
         <v>18</v>
       </c>
-      <c r="C22" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="13" t="s">
+      <c r="C22" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>47</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>103</v>
+      <c r="F22" s="10" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="23" ht="49.25" customHeight="1">
-      <c r="A23" s="22">
+      <c r="A23" s="17">
         <f t="shared" si="10"/>
         <v>45401</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="9">
         <v>19</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>85</v>
+      <c r="C23" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>84</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>85</v>
+      <c r="F23" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="24" ht="94" customHeight="1">
-      <c r="A24" s="22">
+      <c r="A24" s="17">
         <f t="shared" si="10"/>
         <v>45406</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="9">
         <v>20</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>71</v>
+      <c r="C24" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="13" t="s">
-        <v>104</v>
+      <c r="F24" s="10" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="25" ht="55.950000000000003" customHeight="1">
-      <c r="A25" s="22">
+      <c r="A25" s="17">
         <f t="shared" si="10"/>
         <v>45408</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="9">
         <v>21</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>85</v>
+      <c r="C25" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>84</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="13" t="s">
-        <v>85</v>
+      <c r="F25" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="26" ht="79.099999999999994" customHeight="1">
-      <c r="A26" s="22">
+      <c r="A26" s="17">
         <f t="shared" si="10"/>
         <v>45413</v>
       </c>
       <c r="B26" s="4">
         <v>22</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E26" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="F26" s="9"/>
+      <c r="E26" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="7"/>
     </row>
     <row r="27" ht="89.549999999999997" customHeight="1">
-      <c r="A27" s="22">
+      <c r="A27" s="17">
         <f t="shared" si="10"/>
         <v>45415</v>
       </c>
       <c r="B27" s="4">
         <v>23</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="8" t="s">
         <v>37</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>105</v>
+      <c r="F27" s="8" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="28" ht="69.400000000000006" customHeight="1">
-      <c r="A28" s="22">
+      <c r="A28" s="17">
         <f t="shared" si="10"/>
         <v>45420</v>
       </c>
       <c r="B28" s="4">
         <v>24</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="8" t="s">
         <v>39</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>106</v>
+      <c r="F28" s="8" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="29" ht="13.800000000000001" customHeight="1">
-      <c r="A29" s="22">
+      <c r="A29" s="17">
         <f t="shared" si="10"/>
         <v>45422</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="22">
+      <c r="A30" s="17">
         <f t="shared" si="10"/>
         <v>45427</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
     </row>
     <row r="1048574" ht="12.800000000000001"/>
     <row r="1048575" ht="12.800000000000001"/>
@@ -4811,23 +4752,23 @@
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" ht="68.650000000000006">
-      <c r="A2" s="22">
+      <c r="A2" s="17">
         <v>45329</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -4841,13 +4782,13 @@
       </c>
     </row>
     <row r="3" ht="55.200000000000003">
-      <c r="A3" s="22">
+      <c r="A3" s="17">
         <v>45331</v>
       </c>
       <c r="B3" s="4">
         <v>2</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -4861,31 +4802,31 @@
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="22">
+      <c r="A4" s="17">
         <f t="shared" ref="A4:A11" si="11">A2+7</f>
         <v>45336</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="7"/>
+      <c r="C4" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" s="9"/>
+      <c r="E4" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" ht="55.200000000000003">
-      <c r="A5" s="22">
+      <c r="A5" s="17">
         <f t="shared" si="11"/>
         <v>45338</v>
       </c>
       <c r="B5" s="4">
         <v>3</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -4897,318 +4838,318 @@
       <c r="F5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="38" t="s">
-        <v>107</v>
+      <c r="G5" s="33" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="6" ht="68.650000000000006">
-      <c r="A6" s="22">
+      <c r="A6" s="17">
         <f t="shared" si="11"/>
         <v>45343</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="9">
         <v>4</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>109</v>
-      </c>
     </row>
     <row r="7" ht="95.5">
-      <c r="A7" s="22">
+      <c r="A7" s="17">
         <f t="shared" si="11"/>
         <v>45345</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="9">
         <v>5</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="10" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>110</v>
+      <c r="F7" s="10" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="8" ht="144.75" customHeight="1">
-      <c r="A8" s="22">
+      <c r="A8" s="17">
         <f t="shared" si="11"/>
         <v>45350</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <v>6</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>112</v>
-      </c>
     </row>
     <row r="9" ht="155.25" customHeight="1">
-      <c r="A9" s="22">
+      <c r="A9" s="17">
         <f t="shared" si="11"/>
         <v>45352</v>
       </c>
       <c r="B9" s="4">
         <v>7</v>
       </c>
-      <c r="C9" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="10" t="s">
+      <c r="C9" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>92</v>
+      <c r="F9" s="8" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="10" ht="101.25" customHeight="1">
-      <c r="A10" s="22">
+      <c r="A10" s="17">
         <f t="shared" si="11"/>
         <v>45357</v>
       </c>
       <c r="B10" s="4">
         <v>8</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>114</v>
-      </c>
     </row>
     <row r="11" ht="88.5" customHeight="1">
-      <c r="A11" s="22">
+      <c r="A11" s="17">
         <f t="shared" si="11"/>
         <v>45359</v>
       </c>
       <c r="B11" s="4">
         <v>9</v>
       </c>
-      <c r="C11" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>76</v>
+      <c r="C11" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>115</v>
+      <c r="F11" s="8" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="12" ht="75" customHeight="1">
-      <c r="A12" s="22">
+      <c r="A12" s="17">
         <f t="shared" ref="A12:A30" si="12">A10+7</f>
         <v>45364</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="9">
         <v>10</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>117</v>
-      </c>
     </row>
     <row r="13" ht="74.599999999999994" customHeight="1">
-      <c r="A13" s="22">
+      <c r="A13" s="17">
         <f t="shared" si="12"/>
         <v>45366</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="20" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="10" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="13" t="s">
-        <v>98</v>
+      <c r="F13" s="10" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="14" ht="81.299999999999997" customHeight="1">
-      <c r="A14" s="22">
+      <c r="A14" s="17">
         <f t="shared" si="12"/>
         <v>45371</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="20" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="10" t="s">
         <v>28</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>99</v>
+      <c r="F14" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" ht="103.7" customHeight="1">
-      <c r="A15" s="22">
+      <c r="A15" s="17">
         <f t="shared" si="12"/>
         <v>45373</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="9">
         <v>11</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="19"/>
+      <c r="C15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="15"/>
     </row>
     <row r="16" ht="79.5" customHeight="1">
-      <c r="A16" s="22">
+      <c r="A16" s="17">
         <f t="shared" si="12"/>
         <v>45378</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="9">
         <v>12</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="19"/>
+      <c r="C16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="15"/>
       <c r="I16" s="4">
         <v>12</v>
       </c>
-      <c r="J16" s="28" t="s">
+      <c r="J16" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="K16" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="L16" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="L16" s="5" t="s">
-        <v>121</v>
-      </c>
     </row>
     <row r="17" ht="93" customHeight="1">
-      <c r="A17" s="22">
+      <c r="A17" s="17">
         <f t="shared" si="12"/>
         <v>45380</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="9">
         <v>13</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17" s="9"/>
+      <c r="E17" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" ht="55.200000000000003">
-      <c r="A18" s="22">
+      <c r="A18" s="17">
         <f t="shared" si="12"/>
         <v>45385</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="9">
         <v>14</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>30</v>
+      <c r="D18" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="13" t="s">
-        <v>100</v>
+      <c r="F18" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="19" ht="28.350000000000001">
-      <c r="A19" s="22">
+      <c r="A19" s="17">
         <f t="shared" si="12"/>
         <v>45387</v>
       </c>
       <c r="B19" s="4">
         <v>15</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>102</v>
-      </c>
     </row>
     <row r="20" ht="72.75" customHeight="1">
-      <c r="A20" s="22">
+      <c r="A20" s="17">
         <f t="shared" si="12"/>
         <v>45392</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="9">
         <v>16</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="5" t="s">
@@ -5222,209 +5163,209 @@
       </c>
     </row>
     <row r="21" ht="68.650000000000006">
-      <c r="A21" s="22">
+      <c r="A21" s="17">
         <f t="shared" si="12"/>
         <v>45394</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="9">
         <v>17</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="13" t="s">
+      <c r="C21" s="16" t="s">
         <v>44</v>
       </c>
+      <c r="D21" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="E21" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="13" t="s">
-        <v>45</v>
+      <c r="F21" s="10" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="22" ht="41" customHeight="1">
-      <c r="A22" s="22">
+      <c r="A22" s="17">
         <f t="shared" si="12"/>
         <v>45399</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="9">
         <v>18</v>
       </c>
-      <c r="C22" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="13" t="s">
+      <c r="C22" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>47</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="G22" s="38" t="s">
-        <v>107</v>
+      <c r="F22" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G22" s="33" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="22">
+      <c r="A23" s="17">
         <f t="shared" si="12"/>
         <v>45401</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="9">
         <v>19</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>85</v>
+      <c r="C23" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>84</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>85</v>
+      <c r="F23" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="24" ht="39.549999999999997" customHeight="1">
-      <c r="A24" s="22">
+      <c r="A24" s="17">
         <f t="shared" si="12"/>
         <v>45406</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="9">
         <v>20</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>71</v>
+      <c r="C24" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="13" t="s">
-        <v>104</v>
+      <c r="F24" s="10" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="25" ht="42.5" customHeight="1">
-      <c r="A25" s="22">
+      <c r="A25" s="17">
         <f t="shared" si="12"/>
         <v>45408</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="9">
         <v>21</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>85</v>
+      <c r="C25" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>84</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="G25" s="38" t="s">
-        <v>107</v>
+      <c r="F25" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" s="33" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="26" ht="79.099999999999994" customHeight="1">
-      <c r="A26" s="22">
+      <c r="A26" s="17">
         <f t="shared" si="12"/>
         <v>45413</v>
       </c>
       <c r="B26" s="4">
         <v>22</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E26" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="F26" s="9"/>
+      <c r="E26" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="7"/>
     </row>
     <row r="27" ht="89.549999999999997" customHeight="1">
-      <c r="A27" s="22">
+      <c r="A27" s="17">
         <f t="shared" si="12"/>
         <v>45415</v>
       </c>
       <c r="B27" s="4">
         <v>23</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="8" t="s">
         <v>37</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>105</v>
+      <c r="F27" s="8" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="28" ht="69.400000000000006" customHeight="1">
-      <c r="A28" s="22">
+      <c r="A28" s="17">
         <f t="shared" si="12"/>
         <v>45420</v>
       </c>
       <c r="B28" s="4">
         <v>24</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="8" t="s">
         <v>39</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G28" s="38" t="s">
-        <v>122</v>
+      <c r="F28" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="G28" s="33" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="29" ht="13.800000000000001" customHeight="1">
-      <c r="A29" s="22">
+      <c r="A29" s="17">
         <f t="shared" si="12"/>
         <v>45422</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="22">
+      <c r="A30" s="17">
         <f t="shared" si="12"/>
         <v>45427</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
     </row>
     <row r="1048574" ht="12.800000000000001"/>
     <row r="1048575" ht="12.800000000000001"/>
@@ -5471,23 +5412,23 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" ht="68.650000000000006">
-      <c r="A2" s="22">
+      <c r="A2" s="17">
         <v>44965</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -5498,13 +5439,13 @@
       </c>
     </row>
     <row r="3" ht="55.200000000000003">
-      <c r="A3" s="22">
+      <c r="A3" s="17">
         <v>44967</v>
       </c>
       <c r="B3" s="4">
         <v>2</v>
       </c>
-      <c r="C3" s="10"/>
+      <c r="C3" s="8"/>
       <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
@@ -5513,442 +5454,442 @@
       </c>
     </row>
     <row r="4" ht="55.200000000000003">
-      <c r="A4" s="22">
+      <c r="A4" s="17">
         <f t="shared" ref="A4:A11" si="13">A2+7</f>
         <v>44972</v>
       </c>
       <c r="B4" s="4">
         <v>3</v>
       </c>
-      <c r="C4" s="10"/>
+      <c r="C4" s="8"/>
       <c r="D4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="39" t="s">
-        <v>123</v>
+      <c r="F4" s="34" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="5" ht="28.350000000000001">
-      <c r="A5" s="22">
+      <c r="A5" s="17">
         <f t="shared" si="13"/>
         <v>44974</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="9">
         <v>4</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>125</v>
-      </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="22">
+      <c r="A6" s="17">
         <f t="shared" si="13"/>
         <v>44979</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="B6" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
     </row>
     <row r="7" ht="28.350000000000001">
-      <c r="A7" s="22">
+      <c r="A7" s="17">
         <f t="shared" si="13"/>
         <v>44981</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="9">
         <v>5</v>
       </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="13" t="s">
+      <c r="C7" s="35"/>
+      <c r="D7" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="E7" s="13" t="s">
-        <v>127</v>
-      </c>
     </row>
     <row r="8" ht="102" customHeight="1">
-      <c r="A8" s="22">
+      <c r="A8" s="17">
         <f t="shared" si="13"/>
         <v>44986</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <v>6</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="13" t="s">
+      <c r="C8" s="35"/>
+      <c r="D8" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>129</v>
-      </c>
     </row>
     <row r="9" ht="155.25" customHeight="1">
-      <c r="A9" s="22">
+      <c r="A9" s="17">
         <f t="shared" si="13"/>
         <v>44988</v>
       </c>
       <c r="B9" s="4">
         <v>7</v>
       </c>
-      <c r="C9" s="28" t="s">
-        <v>130</v>
+      <c r="C9" s="23" t="s">
+        <v>129</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" ht="101.25" customHeight="1">
-      <c r="A10" s="22">
+      <c r="A10" s="17">
         <f t="shared" si="13"/>
         <v>44993</v>
       </c>
       <c r="B10" s="4">
         <v>8</v>
       </c>
-      <c r="C10" s="28"/>
+      <c r="C10" s="23"/>
       <c r="D10" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="11" ht="88.5" customHeight="1">
-      <c r="A11" s="22">
+      <c r="A11" s="17">
         <f t="shared" si="13"/>
         <v>44995</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="9">
         <v>9</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>98</v>
+      <c r="E11" s="10" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="12" ht="75" customHeight="1">
-      <c r="A12" s="22">
+      <c r="A12" s="17">
         <f t="shared" ref="A12:A33" si="14">A10+7</f>
         <v>45000</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="9">
         <v>10</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="13" t="s">
+      <c r="C12" s="16"/>
+      <c r="D12" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="13" t="s">
-        <v>99</v>
+      <c r="E12" s="10" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="13" ht="55.200000000000003">
-      <c r="A13" s="22">
+      <c r="A13" s="17">
         <f t="shared" si="14"/>
         <v>45002</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="9">
         <v>11</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>100</v>
+      <c r="C13" s="16"/>
+      <c r="D13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="22">
+      <c r="A14" s="17">
         <f t="shared" si="14"/>
         <v>45007</v>
       </c>
-      <c r="B14" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
+      <c r="B14" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="22">
+      <c r="A15" s="17">
         <f t="shared" si="14"/>
         <v>45009</v>
       </c>
-      <c r="B15" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
+      <c r="B15" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
     </row>
     <row r="16" ht="79.5" customHeight="1">
-      <c r="A16" s="22">
+      <c r="A16" s="17">
         <f t="shared" si="14"/>
         <v>45014</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="9">
         <v>12</v>
       </c>
-      <c r="C16" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="D16" s="13" t="s">
+      <c r="C16" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>92</v>
+      <c r="E16" s="10" t="s">
+        <v>91</v>
       </c>
       <c r="H16" s="4">
         <v>12</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I16" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="K16" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="K16" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="L16" s="39" t="s">
-        <v>123</v>
+      <c r="L16" s="34" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="17" ht="93" customHeight="1">
-      <c r="A17" s="22">
+      <c r="A17" s="17">
         <f t="shared" si="14"/>
         <v>45016</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="9">
         <v>13</v>
       </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="13" t="s">
+      <c r="C17" s="35"/>
+      <c r="D17" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="42" t="s">
-        <v>134</v>
+      <c r="E17" s="37" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="22">
+      <c r="A18" s="17">
         <f t="shared" si="14"/>
         <v>45021</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="B18" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="22">
+      <c r="A19" s="17">
         <f t="shared" si="14"/>
         <v>45023</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="B19" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
     </row>
     <row r="20" ht="72.75" customHeight="1">
-      <c r="A20" s="22">
+      <c r="A20" s="17">
         <f t="shared" si="14"/>
         <v>45028</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="9">
         <v>14</v>
       </c>
-      <c r="C20" s="40"/>
-      <c r="D20" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="F20" s="39" t="s">
-        <v>123</v>
+      <c r="C20" s="35"/>
+      <c r="D20" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="21" ht="68.650000000000006">
-      <c r="A21" s="22">
+      <c r="A21" s="17">
         <f t="shared" si="14"/>
         <v>45030</v>
       </c>
       <c r="B21" s="4">
         <v>15</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>136</v>
+      <c r="C21" s="8" t="s">
+        <v>135</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" ht="95.5">
-      <c r="A22" s="22">
+      <c r="A22" s="17">
         <f t="shared" si="14"/>
         <v>45035</v>
       </c>
       <c r="B22" s="4">
         <v>16</v>
       </c>
-      <c r="C22" s="10"/>
+      <c r="C22" s="8"/>
       <c r="D22" s="5" t="s">
         <v>47</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="22">
+      <c r="A23" s="17">
         <f t="shared" si="14"/>
         <v>45037</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="B23" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
     </row>
     <row r="24" ht="95.5">
-      <c r="A24" s="22">
+      <c r="A24" s="17">
         <f t="shared" si="14"/>
         <v>45042</v>
       </c>
       <c r="B24" s="4">
         <v>17</v>
       </c>
-      <c r="C24" s="10"/>
+      <c r="C24" s="8"/>
       <c r="D24" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" ht="41.75">
-      <c r="A25" s="22">
+      <c r="A25" s="17">
         <f t="shared" si="14"/>
         <v>45044</v>
       </c>
       <c r="B25" s="4">
         <v>18</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="8"/>
       <c r="D25" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="26" ht="57.450000000000003" customHeight="1">
-      <c r="A26" s="22">
+      <c r="A26" s="17">
         <f t="shared" si="14"/>
         <v>45049</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="9">
         <v>19</v>
       </c>
-      <c r="C26" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="D26" s="13" t="s">
+      <c r="C26" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="13" t="s">
-        <v>105</v>
+      <c r="E26" s="10" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="27" ht="68.650000000000006">
-      <c r="A27" s="22">
+      <c r="A27" s="17">
         <f t="shared" si="14"/>
         <v>45051</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="9">
         <v>20</v>
       </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="13" t="s">
-        <v>106</v>
+      <c r="C27" s="16"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="10" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="28" ht="41.75">
-      <c r="A28" s="22">
+      <c r="A28" s="17">
         <f t="shared" si="14"/>
         <v>45056</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="9">
         <v>21</v>
       </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="13" t="s">
-        <v>141</v>
+      <c r="C28" s="16"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="10" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="29" ht="14.25">
-      <c r="A29" s="22">
+      <c r="A29" s="17">
         <f t="shared" si="14"/>
         <v>45058</v>
       </c>
-      <c r="B29" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
+      <c r="B29" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="22">
+      <c r="A30" s="17">
         <f t="shared" si="14"/>
         <v>45063</v>
       </c>
     </row>
     <row r="31" ht="14.25">
-      <c r="A31" s="22">
+      <c r="A31" s="17">
         <f t="shared" si="14"/>
         <v>45065</v>
       </c>
     </row>
     <row r="32" ht="14.25">
-      <c r="A32" s="22">
+      <c r="A32" s="17">
         <f t="shared" si="14"/>
         <v>45070</v>
       </c>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="22">
+      <c r="A33" s="17">
         <f t="shared" si="14"/>
         <v>45072</v>
       </c>
